--- a/RPC-Matriz-de-precios.xlsx
+++ b/RPC-Matriz-de-precios.xlsx
@@ -759,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2260,8 +2260,152 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="B43" s="17" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="16" t="inlineStr"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Jeans</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>15990</v>
+      </c>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="12" t="n">
+        <v>12990</v>
+      </c>
+      <c r="J42" s="13" t="n"/>
+      <c r="K42" s="13" t="n"/>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="14" t="n"/>
+      <c r="N42" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 38-60 · mezclilla azul · hombre y mujer</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="16" t="inlineStr"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Outdoor</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G43" s="13" t="n"/>
+      <c r="H43" s="13" t="n"/>
+      <c r="I43" s="12" t="n">
+        <v>23990</v>
+      </c>
+      <c r="J43" s="13" t="n"/>
+      <c r="K43" s="13" t="n"/>
+      <c r="L43" s="13" t="n"/>
+      <c r="M43" s="14" t="n"/>
+      <c r="N43" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 38-60 · tela ripstop · hombre y mujer separados</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="16" t="inlineStr"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Gabardina Spandex</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>17500</v>
+      </c>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="13" t="n"/>
+      <c r="I44" s="12" t="n">
+        <v>14500</v>
+      </c>
+      <c r="J44" s="13" t="n"/>
+      <c r="K44" s="13" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="14" t="n"/>
+      <c r="N44" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 36-58 · 97% algodón + 3% spandex · mujer (también hay hombre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="16" t="inlineStr"/>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Pinza Hombre</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>17500</v>
+      </c>
+      <c r="G45" s="13" t="n"/>
+      <c r="H45" s="13" t="n"/>
+      <c r="I45" s="12" t="n">
+        <v>14500</v>
+      </c>
+      <c r="J45" s="13" t="n"/>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="14" t="n"/>
+      <c r="N45" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 40-64 · 100% algodón · formal hombre</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>Celdas celestes = tope y piso del rango que ustedes entregaron en el formulario; sólo confirmar/ajustar. Celdas amarillas = precios intermedios y a granel a completar. Si un tramo no aplica, déjalo en blanco.</t>
         </is>
@@ -2269,10 +2413,10 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B43:N43"/>
+    <mergeCell ref="B47:N47"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="M4:M41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Elige Neto o Con IVA" promptTitle="IVA" prompt="Indica si el precio está en neto o con IVA" type="list">
+    <dataValidation sqref="M4:M45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Elige Neto o Con IVA" promptTitle="IVA" prompt="Indica si el precio está en neto o con IVA" type="list">
       <formula1>"Neto (+IVA),Con IVA incluido"</formula1>
     </dataValidation>
   </dataValidations>

--- a/RPC-Matriz-de-precios.xlsx
+++ b/RPC-Matriz-de-precios.xlsx
@@ -759,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2152,31 +2152,27 @@
       <c r="A39" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Pantalones</t>
-        </is>
-      </c>
+      <c r="B39" s="16" t="inlineStr"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Pantalón Cargo Gabardina</t>
+          <t>Mandil Largo Poliéster</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Stock express</t>
+          <t>Fabricación a medida</t>
         </is>
       </c>
       <c r="E39" s="10" t="n">
         <v>10</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>16990</v>
+        <v>9900</v>
       </c>
       <c r="G39" s="13" t="n"/>
       <c r="H39" s="13" t="n"/>
       <c r="I39" s="12" t="n">
-        <v>13990</v>
+        <v>6990</v>
       </c>
       <c r="J39" s="13" t="n"/>
       <c r="K39" s="13" t="n"/>
@@ -2184,7 +2180,7 @@
       <c r="M39" s="14" t="n"/>
       <c r="N39" s="15" t="inlineStr">
         <is>
-          <t>Cintura 38-58 · hombre y mujer · opción sin logo</t>
+          <t>100% poliéster · 10-15 días confección / 3-7 días stock</t>
         </is>
       </c>
     </row>
@@ -2195,24 +2191,24 @@
       <c r="B40" s="16" t="inlineStr"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Pantalón Recto Tipo Docker</t>
+          <t>Gorro de Chef</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Stock express</t>
+          <t>Fabricación a medida</t>
         </is>
       </c>
       <c r="E40" s="10" t="n">
         <v>10</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>16990</v>
+        <v>7990</v>
       </c>
       <c r="G40" s="13" t="n"/>
       <c r="H40" s="13" t="n"/>
       <c r="I40" s="12" t="n">
-        <v>13990</v>
+        <v>5500</v>
       </c>
       <c r="J40" s="13" t="n"/>
       <c r="K40" s="13" t="n"/>
@@ -2220,7 +2216,7 @@
       <c r="M40" s="14" t="n"/>
       <c r="N40" s="15" t="inlineStr">
         <is>
-          <t>Cintura 38-58 · hombre y mujer · opción sin logo</t>
+          <t>Polycron · un color o bicolor</t>
         </is>
       </c>
     </row>
@@ -2231,24 +2227,24 @@
       <c r="B41" s="16" t="inlineStr"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Pantalón Cargo Poplin</t>
+          <t>Cofia</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Stock express</t>
+          <t>Fabricación a medida</t>
         </is>
       </c>
       <c r="E41" s="10" t="n">
         <v>10</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>13900</v>
+        <v>6990</v>
       </c>
       <c r="G41" s="13" t="n"/>
       <c r="H41" s="13" t="n"/>
       <c r="I41" s="12" t="n">
-        <v>8990</v>
+        <v>3990</v>
       </c>
       <c r="J41" s="13" t="n"/>
       <c r="K41" s="13" t="n"/>
@@ -2256,7 +2252,7 @@
       <c r="M41" s="14" t="n"/>
       <c r="N41" s="15" t="inlineStr">
         <is>
-          <t>Tallas S-2XL · modelo unisex</t>
+          <t>Un color o bicolor</t>
         </is>
       </c>
     </row>
@@ -2264,10 +2260,14 @@
       <c r="A42" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="16" t="inlineStr"/>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Jockeys, Gorros y Accesorios</t>
+        </is>
+      </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Pantalón Jeans</t>
+          <t>Jockey Gabardina para Estampado</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -2276,15 +2276,15 @@
         </is>
       </c>
       <c r="E42" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>15990</v>
+        <v>6900</v>
       </c>
       <c r="G42" s="13" t="n"/>
       <c r="H42" s="13" t="n"/>
       <c r="I42" s="12" t="n">
-        <v>12990</v>
+        <v>3990</v>
       </c>
       <c r="J42" s="13" t="n"/>
       <c r="K42" s="13" t="n"/>
@@ -2292,7 +2292,7 @@
       <c r="M42" s="14" t="n"/>
       <c r="N42" s="15" t="inlineStr">
         <is>
-          <t>Cintura 38-60 · mezclilla azul · hombre y mujer</t>
+          <t>Mín 12 u · todos los colores · frente liso para estampado</t>
         </is>
       </c>
     </row>
@@ -2300,10 +2300,14 @@
       <c r="A43" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="16" t="inlineStr"/>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Pantalones</t>
+        </is>
+      </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Pantalón Outdoor</t>
+          <t>Pantalón Cargo Gabardina</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -2315,12 +2319,12 @@
         <v>10</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>26900</v>
+        <v>16990</v>
       </c>
       <c r="G43" s="13" t="n"/>
       <c r="H43" s="13" t="n"/>
       <c r="I43" s="12" t="n">
-        <v>23990</v>
+        <v>13990</v>
       </c>
       <c r="J43" s="13" t="n"/>
       <c r="K43" s="13" t="n"/>
@@ -2328,7 +2332,7 @@
       <c r="M43" s="14" t="n"/>
       <c r="N43" s="15" t="inlineStr">
         <is>
-          <t>Cintura 38-60 · tela ripstop · hombre y mujer separados</t>
+          <t>Cintura 38-58 · hombre y mujer · opción sin logo</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2343,7 @@
       <c r="B44" s="16" t="inlineStr"/>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Pantalón Gabardina Spandex</t>
+          <t>Pantalón Recto Tipo Docker</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -2351,12 +2355,12 @@
         <v>10</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>17500</v>
+        <v>16990</v>
       </c>
       <c r="G44" s="13" t="n"/>
       <c r="H44" s="13" t="n"/>
       <c r="I44" s="12" t="n">
-        <v>14500</v>
+        <v>13990</v>
       </c>
       <c r="J44" s="13" t="n"/>
       <c r="K44" s="13" t="n"/>
@@ -2364,7 +2368,7 @@
       <c r="M44" s="14" t="n"/>
       <c r="N44" s="15" t="inlineStr">
         <is>
-          <t>Cintura 36-58 · 97% algodón + 3% spandex · mujer (también hay hombre)</t>
+          <t>Cintura 38-58 · hombre y mujer · opción sin logo</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2379,7 @@
       <c r="B45" s="16" t="inlineStr"/>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Pantalón Pinza Hombre</t>
+          <t>Pantalón Cargo Poplin</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -2387,12 +2391,12 @@
         <v>10</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>17500</v>
+        <v>13900</v>
       </c>
       <c r="G45" s="13" t="n"/>
       <c r="H45" s="13" t="n"/>
       <c r="I45" s="12" t="n">
-        <v>14500</v>
+        <v>8990</v>
       </c>
       <c r="J45" s="13" t="n"/>
       <c r="K45" s="13" t="n"/>
@@ -2400,12 +2404,192 @@
       <c r="M45" s="14" t="n"/>
       <c r="N45" s="15" t="inlineStr">
         <is>
+          <t>Tallas S-2XL · modelo unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="16" t="inlineStr"/>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Jeans</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>15990</v>
+      </c>
+      <c r="G46" s="13" t="n"/>
+      <c r="H46" s="13" t="n"/>
+      <c r="I46" s="12" t="n">
+        <v>12990</v>
+      </c>
+      <c r="J46" s="13" t="n"/>
+      <c r="K46" s="13" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="14" t="n"/>
+      <c r="N46" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 38-60 · mezclilla azul · hombre y mujer</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="16" t="inlineStr"/>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Outdoor</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>26900</v>
+      </c>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="13" t="n"/>
+      <c r="I47" s="12" t="n">
+        <v>23990</v>
+      </c>
+      <c r="J47" s="13" t="n"/>
+      <c r="K47" s="13" t="n"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="14" t="n"/>
+      <c r="N47" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 38-60 · tela ripstop · hombre y mujer separados</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="16" t="inlineStr"/>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Gabardina Spandex</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>17500</v>
+      </c>
+      <c r="G48" s="13" t="n"/>
+      <c r="H48" s="13" t="n"/>
+      <c r="I48" s="12" t="n">
+        <v>14500</v>
+      </c>
+      <c r="J48" s="13" t="n"/>
+      <c r="K48" s="13" t="n"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="14" t="n"/>
+      <c r="N48" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 36-58 · 97% algodón + 3% spandex · mujer (también hay hombre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="16" t="inlineStr"/>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Pinza Hombre</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>17500</v>
+      </c>
+      <c r="G49" s="13" t="n"/>
+      <c r="H49" s="13" t="n"/>
+      <c r="I49" s="12" t="n">
+        <v>14500</v>
+      </c>
+      <c r="J49" s="13" t="n"/>
+      <c r="K49" s="13" t="n"/>
+      <c r="L49" s="13" t="n"/>
+      <c r="M49" s="14" t="n"/>
+      <c r="N49" s="15" t="inlineStr">
+        <is>
           <t>Cintura 40-64 · 100% algodón · formal hombre</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="B47" s="17" t="inlineStr">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="16" t="inlineStr"/>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Cargo Forro Polar</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G50" s="13" t="n"/>
+      <c r="H50" s="13" t="n"/>
+      <c r="I50" s="12" t="n">
+        <v>14500</v>
+      </c>
+      <c r="J50" s="13" t="n"/>
+      <c r="K50" s="13" t="n"/>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="14" t="n"/>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 40-60 · gabardina con forro polar · invierno · hombre y mujer</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>Celdas celestes = tope y piso del rango que ustedes entregaron en el formulario; sólo confirmar/ajustar. Celdas amarillas = precios intermedios y a granel a completar. Si un tramo no aplica, déjalo en blanco.</t>
         </is>
@@ -2413,10 +2597,10 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B47:N47"/>
+    <mergeCell ref="B52:N52"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="M4:M45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Elige Neto o Con IVA" promptTitle="IVA" prompt="Indica si el precio está en neto o con IVA" type="list">
+    <dataValidation sqref="M4:M50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Elige Neto o Con IVA" promptTitle="IVA" prompt="Indica si el precio está en neto o con IVA" type="list">
       <formula1>"Neto (+IVA),Con IVA incluido"</formula1>
     </dataValidation>
   </dataValidations>
